--- a/documents/Työajan seuranta.xlsx
+++ b/documents/Työajan seuranta.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29721"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unioulu-my.sharepoint.com/personal/jukkanev_oamk_fi/Documents/Opintojaksot/Kevät 2026/Mobiilikehitysprojekti IN00ED17/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\codes\mobile-project\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B51462E0-F020-4DC2-AA82-B103E227914D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDA526C5-F43A-4776-81B2-3046648D544B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-10680" yWindow="-19680" windowWidth="38700" windowHeight="15285" activeTab="1" xr2:uid="{B7036960-D674-4B76-B564-D076AACD5E6B}"/>
+    <workbookView xWindow="4143" yWindow="4143" windowWidth="26083" windowHeight="13830" activeTab="1" xr2:uid="{B7036960-D674-4B76-B564-D076AACD5E6B}"/>
   </bookViews>
   <sheets>
     <sheet name="Niko Pippuri" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="62">
   <si>
     <t>Ryhmä:</t>
   </si>
@@ -106,6 +106,18 @@
     <t>pr hyväksymisiä</t>
   </si>
   <si>
+    <t>notifikaattien tekoa</t>
+  </si>
+  <si>
+    <t>expo eas cloud buildin tekoa</t>
+  </si>
+  <si>
+    <t>uudestaan notifikaattien tekoa</t>
+  </si>
+  <si>
+    <t>Yhteensä:</t>
+  </si>
+  <si>
     <t>Samuli Kokko</t>
   </si>
   <si>
@@ -154,6 +166,15 @@
     <t>Liiketoimintasuunnitelman ja laskelmien tekoa</t>
   </si>
   <si>
+    <t>Password management koodausta sovelluskeen</t>
+  </si>
+  <si>
+    <t>Matikan poster</t>
+  </si>
+  <si>
+    <t>Loppuesitysvideo, pisteytyslomake</t>
+  </si>
+  <si>
     <t>Nico Lappalainen</t>
   </si>
   <si>
@@ -200,14 +221,25 @@
   </si>
   <si>
     <t>Merge confliktit</t>
+  </si>
+  <si>
+    <t>UI teeman refaktorointi, tumman teeman lisäys + assessments</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -223,7 +255,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -240,14 +272,29 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normaali" xfId="0" builtinId="0"/>
@@ -266,9 +313,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022 -teema">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -306,7 +353,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -412,7 +459,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -554,7 +601,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -562,15 +609,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BD4D073-EB2D-44A2-86BF-660E3721AF80}">
-  <dimension ref="A1:C22"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <dimension ref="A1:C26"/>
+  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" customWidth="1"/>
-    <col min="2" max="2" width="34.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="6" width="13.28515625" customWidth="1"/>
+    <col min="1" max="1" width="9.75" customWidth="1"/>
+    <col min="2" max="2" width="34.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="13.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -578,7 +625,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -589,7 +636,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>46030</v>
       </c>
@@ -600,7 +647,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>46031</v>
       </c>
@@ -611,7 +658,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>46032</v>
       </c>
@@ -622,7 +669,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>46039</v>
       </c>
@@ -633,7 +680,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>46041</v>
       </c>
@@ -644,7 +691,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>46042</v>
       </c>
@@ -655,7 +702,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>46043</v>
       </c>
@@ -666,7 +713,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>46046</v>
       </c>
@@ -677,7 +724,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>46047</v>
       </c>
@@ -688,7 +735,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>46053</v>
       </c>
@@ -699,7 +746,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>46055</v>
       </c>
@@ -710,7 +757,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>46056</v>
       </c>
@@ -721,7 +768,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>46058</v>
       </c>
@@ -732,7 +779,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>46059</v>
       </c>
@@ -743,7 +790,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>46061</v>
       </c>
@@ -754,7 +801,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>45697</v>
       </c>
@@ -765,7 +812,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>45698</v>
       </c>
@@ -776,7 +823,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>46064</v>
       </c>
@@ -787,7 +834,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>46067</v>
       </c>
@@ -798,7 +845,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>46069</v>
       </c>
@@ -807,6 +854,48 @@
       </c>
       <c r="C22">
         <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>46070</v>
+      </c>
+      <c r="B23" t="s">
+        <v>22</v>
+      </c>
+      <c r="C23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>46071</v>
+      </c>
+      <c r="B24" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>46072</v>
+      </c>
+      <c r="B25" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C26">
+        <f>SUM(C3:C25)</f>
+        <v>56.5</v>
       </c>
     </row>
   </sheetData>
@@ -816,15 +905,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74BC3D70-9A8B-4A59-8343-1D3356DFB267}">
-  <dimension ref="A1:C37"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <dimension ref="A1:C33"/>
+  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" customWidth="1"/>
-    <col min="2" max="2" width="41.28515625" customWidth="1"/>
+    <col min="1" max="1" width="9.75" customWidth="1"/>
+    <col min="2" max="2" width="41.25" customWidth="1"/>
     <col min="3" max="3" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -832,7 +921,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -840,349 +929,365 @@
         <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>46030</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>46031</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C4">
         <v>1.5</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>46031</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C5">
         <v>0.5</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>46032</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C6">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>46032</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>46034</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>46038</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C9">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>46039</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C10">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>46043</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C11">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>46045</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C12">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>46046</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C13">
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>46050</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C14">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>46055</v>
       </c>
       <c r="B15" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C15">
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>46056</v>
       </c>
       <c r="B16" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C16">
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>46060</v>
       </c>
       <c r="B17" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C17">
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>46060</v>
       </c>
       <c r="B18" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C18">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>46060</v>
       </c>
       <c r="B19" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C19">
         <v>3.5</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>46061</v>
       </c>
       <c r="B20" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C20">
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>46061</v>
       </c>
       <c r="B21" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C21">
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>46061</v>
       </c>
       <c r="B22" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C22">
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>46062</v>
       </c>
       <c r="B23" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C23">
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>46064</v>
       </c>
       <c r="B24" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C24">
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>46065</v>
       </c>
       <c r="B25" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C25">
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>46066</v>
       </c>
       <c r="B26" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C26">
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>46067</v>
       </c>
       <c r="B27" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C27">
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>46068</v>
       </c>
       <c r="B28" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C28">
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>46070</v>
       </c>
+      <c r="B29" t="s">
+        <v>42</v>
+      </c>
       <c r="C29">
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>46071</v>
       </c>
+      <c r="B30" t="s">
+        <v>42</v>
+      </c>
       <c r="C30">
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>46072</v>
       </c>
+      <c r="B31" t="s">
+        <v>43</v>
+      </c>
       <c r="C31">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="1">
-        <v>46073</v>
-      </c>
-      <c r="C32">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="37" spans="3:3">
-      <c r="C37">
-        <f>SUM(C3:C36)</f>
-        <v>71.5</v>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="5">
+        <v>46074</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C32" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B33" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C33" s="3">
+        <f ca="1">SUM(C3:C36)</f>
+        <v>76.5</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C1EECD9-4AD3-41AF-8923-B28678799497}">
   <dimension ref="A1:C44"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" customWidth="1"/>
-    <col min="2" max="2" width="62.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.75" customWidth="1"/>
+    <col min="2" max="2" width="62.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1190,7 +1295,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1198,255 +1303,272 @@
         <v>2</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>46030</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C3">
         <v>0.5</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>46032</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>46032</v>
       </c>
       <c r="B5" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C5">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>46034</v>
       </c>
       <c r="B6" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C6">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>46036</v>
       </c>
       <c r="B7" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C7">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>46039</v>
       </c>
       <c r="B8" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C8">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>46039</v>
       </c>
       <c r="B9" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="C9">
         <v>0.5</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>46046</v>
       </c>
       <c r="B10" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C10">
         <v>0.5</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>46046</v>
       </c>
       <c r="B11" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C11">
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>46047</v>
       </c>
       <c r="B12" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C12">
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>46049</v>
       </c>
       <c r="B13" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="C13">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>46050</v>
       </c>
       <c r="B14" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C14">
         <v>2.5</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>46053</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="C15">
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>46055</v>
       </c>
       <c r="B16" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C16">
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>46058</v>
       </c>
       <c r="B17" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C17">
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>46061</v>
       </c>
       <c r="B18" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C18">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>46061</v>
       </c>
       <c r="B19" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="C19">
         <v>7.5</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>46062</v>
       </c>
       <c r="B20" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C20">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>46066</v>
       </c>
       <c r="B21" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="C21">
         <v>1.5</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>46067</v>
       </c>
       <c r="B22" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="C22">
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>46068</v>
       </c>
       <c r="B23" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="C23">
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>46070</v>
       </c>
       <c r="B24" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="C24">
         <v>0.5</v>
       </c>
     </row>
-    <row r="44" spans="3:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>46073</v>
+      </c>
+      <c r="B25" t="s">
+        <v>61</v>
+      </c>
+      <c r="C25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C26">
+        <f>SUM(C3:C25)</f>
+        <v>65.5</v>
+      </c>
+    </row>
+    <row r="44" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C44" t="str">
         <f>"Yhteensä:" &amp; " " &amp; SUM(C3:C43) &amp; "h"</f>
-        <v>Yhteensä: 58,5h</v>
+        <v>Yhteensä: 131h</v>
       </c>
     </row>
   </sheetData>
